--- a/Data/Rehires/Workday_Rehire_Romania_Regression_PK17.xlsx
+++ b/Data/Rehires/Workday_Rehire_Romania_Regression_PK17.xlsx
@@ -1,15 +1,29 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
-  <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="27928"/>
+  <workbookPr filterPrivacy="1"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8D3A76DF-15D0-47B5-88DA-A513F012D34B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="10" yWindow="10" windowWidth="19190" windowHeight="10190"/>
+    <workbookView xWindow="10" yWindow="10" windowWidth="19190" windowHeight="10190" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet sheetId="1" name="Test_Data" state="visible" r:id="rId4"/>
+    <sheet name="Test_Data" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="171027"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -211,7 +225,7 @@
     <t>C - Regular labour contract (Romania Contract Types-Romania)@112029@DN - Daylight and Night hours (Romania Time Allocation-Romania)</t>
   </si>
   <si>
-    <t xml:space="preserve">92 Retail Management </t>
+    <t>92 Retail Management </t>
   </si>
   <si>
     <t>251 Management Retail</t>
@@ -223,40 +237,40 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="5" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
       <color theme="1"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color indexed="8"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
       <name val="Calibri"/>
-    </font>
-    <font>
-      <color indexed="8"/>
-      <family val="2"/>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <color rgb="FFFF0000"/>
       <family val="2"/>
       <scheme val="minor"/>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <color rgb="FF000000"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <family val="2"/>
-      <scheme val="minor"/>
-      <sz val="11"/>
-      <name val="Calibri"/>
     </font>
   </fonts>
   <fills count="7">
@@ -268,13 +282,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.5999938962981048"/>
+        <fgColor theme="5" tint="0.59999389629810485"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="0" tint="-0.1499984740745262"/>
+        <fgColor theme="0" tint="-0.14999847407452621"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -285,7 +299,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.7999816888943144"/>
+        <fgColor theme="5" tint="0.79998168889431442"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -311,15 +325,27 @@
       <right style="medium">
         <color indexed="64"/>
       </right>
-      <top style="thin"/>
-      <bottom style="thin"/>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
       <diagonal/>
     </border>
   </borders>
@@ -669,9 +695,9 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:AG3"/>
-  <sheetFormatPr defaultRowHeight="15.65" outlineLevelRow="1" outlineLevelCol="0" x14ac:dyDescent="0.35" customHeight="1"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:BJ3"/>
+  <sheetFormatPr defaultRowHeight="15.65" customHeight="1" outlineLevelRow="1" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="10.90625" style="1" customWidth="1"/>
     <col min="2" max="2" width="10.81640625" style="1" customWidth="1"/>
@@ -736,7 +762,7 @@
     <col min="63" max="63" width="16.08984375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="14.5" customHeight="1" spans="1:33" s="1" customFormat="1" x14ac:dyDescent="0.25" outlineLevel="1" collapsed="1">
+    <row r="1" spans="1:33" s="1" customFormat="1" ht="14.5" customHeight="1" outlineLevel="1" collapsed="1" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -835,7 +861,7 @@
       </c>
       <c r="AG1" s="5"/>
     </row>
-    <row r="2" ht="15.65" customHeight="1" spans="1:32" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:33" s="1" customFormat="1" ht="15.65" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="1" t="s">
         <v>32</v>
       </c>
@@ -861,7 +887,7 @@
         <v>39</v>
       </c>
       <c r="I2" s="11">
-        <f>TODAY()-1</f>
+        <f ca="1">TODAY()-1</f>
         <v>45827</v>
       </c>
       <c r="J2" s="12" t="s">
@@ -892,7 +918,7 @@
         <v>46</v>
       </c>
       <c r="S2" s="16">
-        <f>I2+365</f>
+        <f ca="1">I2+365</f>
         <v>46192</v>
       </c>
       <c r="T2" s="12" t="s">
@@ -911,14 +937,14 @@
         <v>51</v>
       </c>
       <c r="Y2" s="16">
-        <f>I2+180</f>
+        <f ca="1">I2+180</f>
         <v>46007</v>
       </c>
       <c r="Z2" s="14" t="s">
         <v>52</v>
       </c>
       <c r="AA2" s="11">
-        <f>I2-1</f>
+        <f ca="1">I2-1</f>
         <v>45826</v>
       </c>
       <c r="AB2" t="s">
@@ -931,14 +957,14 @@
         <v>54</v>
       </c>
       <c r="AE2" s="11">
-        <f>I2+365</f>
+        <f ca="1">I2+365</f>
         <v>46192</v>
       </c>
       <c r="AF2" s="14" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="3" ht="15.65" customHeight="1" spans="1:32" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:33" s="1" customFormat="1" ht="15.65" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
         <v>55</v>
       </c>
@@ -964,7 +990,7 @@
         <v>59</v>
       </c>
       <c r="I3" s="11">
-        <f>TODAY()-1</f>
+        <f ca="1">TODAY()-1</f>
         <v>45827</v>
       </c>
       <c r="J3" s="12" t="s">
@@ -1013,14 +1039,14 @@
         <v>51</v>
       </c>
       <c r="Y3" s="16">
-        <f>I3+180</f>
+        <f ca="1">I3+180</f>
         <v>46007</v>
       </c>
       <c r="Z3" s="14" t="s">
         <v>52</v>
       </c>
       <c r="AA3" s="11">
-        <f>I3-1</f>
+        <f ca="1">I3-1</f>
         <v>45826</v>
       </c>
       <c r="AB3" t="s">
@@ -1040,22 +1066,16 @@
       </c>
     </row>
   </sheetData>
-  <dataValidations count="4">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AC2:AC3">
+  <dataValidations count="2">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AC2:AC3 O2:O3 J2:J3" xr:uid="{00000000-0002-0000-0000-000000000000}">
       <formula1>INDIRECT($E2)</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="J2:J3">
-      <formula1>INDIRECT($E2)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="O2:O3">
-      <formula1>INDIRECT($E2)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="S3">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="S3" xr:uid="{00000000-0002-0000-0000-000003000000}">
       <formula1>INDIRECT($E2)</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
+  <pageSetup orientation="portrait" useFirstPageNumber="1" horizontalDpi="4294967295" verticalDpi="4294967295"/>
   <headerFooter>
     <oddFooter>&amp;L_x000D_&amp;1#&amp;"Calibri"&amp;10&amp;K000000 EXPLEO Internal</oddFooter>
   </headerFooter>

--- a/Data/Rehires/Workday_Rehire_Romania_Regression_PK17.xlsx
+++ b/Data/Rehires/Workday_Rehire_Romania_Regression_PK17.xlsx
@@ -1,34 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="27928"/>
-  <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8D3A76DF-15D0-47B5-88DA-A513F012D34B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
+  <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
   <bookViews>
-    <workbookView xWindow="10" yWindow="10" windowWidth="19190" windowHeight="10190" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="10" yWindow="10" windowWidth="19190" windowHeight="10190"/>
   </bookViews>
   <sheets>
-    <sheet name="Test_Data" sheetId="1" r:id="rId1"/>
+    <sheet sheetId="1" name="Test_Data" state="visible" r:id="rId4"/>
   </sheets>
-  <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="86" uniqueCount="68">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="86" uniqueCount="70">
   <si>
     <t>TestCaseIDs</t>
   </si>
@@ -129,30 +115,36 @@
     <t>Test1</t>
   </si>
   <si>
+    <t xml:space="preserve">Test failed for 'Cecile Runolfsdottir' Employee:{10699766}TimeoutError: locator.click: Timeout 30000ms exceeded.
+Call log:
+  [2m- waiting for locator('//label[contains(.,\'Hire Date\')]/parent::div/following-sibling::div/descendant::input[@data-automation-id=\'dateSectionDay-input\']')[22m
+</t>
+  </si>
+  <si>
+    <t>Failed</t>
+  </si>
+  <si>
+    <t>Belgium</t>
+  </si>
+  <si>
+    <t>10699766</t>
+  </si>
+  <si>
+    <t>Cecile</t>
+  </si>
+  <si>
+    <t>Runolfsdottir</t>
+  </si>
+  <si>
+    <t>880 Recruitment (Vofur Hagovi (10551546))</t>
+  </si>
+  <si>
+    <t>ReHire</t>
+  </si>
+  <si>
     <t>N/A</t>
   </si>
   <si>
-    <t>Passed</t>
-  </si>
-  <si>
-    <t>Belgium</t>
-  </si>
-  <si>
-    <t>10699766</t>
-  </si>
-  <si>
-    <t>Cecile</t>
-  </si>
-  <si>
-    <t>Runolfsdottir</t>
-  </si>
-  <si>
-    <t>880 Recruitment (Vofur Hagovi (10551546))</t>
-  </si>
-  <si>
-    <t>ReHire</t>
-  </si>
-  <si>
     <t xml:space="preserve">Fixed Term </t>
   </si>
   <si>
@@ -198,6 +190,12 @@
     <t>Test2</t>
   </si>
   <si>
+    <t xml:space="preserve">Test failed for 'Keven Hudson' Employee:{10699767}TimeoutError: locator.click: Timeout 30000ms exceeded.
+Call log:
+  [2m- waiting for locator('//label[contains(.,\'Hire Date\')]/parent::div/following-sibling::div/descendant::input[@data-automation-id=\'dateSectionDay-input\']')[22m
+</t>
+  </si>
+  <si>
     <t>10699767</t>
   </si>
   <si>
@@ -210,7 +208,7 @@
     <t>880 Store Management (Suvug Rozery (10629083))</t>
   </si>
   <si>
-    <t>Auto 69331437</t>
+    <t>Auto 23441288</t>
   </si>
   <si>
     <t>Permanent</t>
@@ -225,7 +223,7 @@
     <t>C - Regular labour contract (Romania Contract Types-Romania)@112029@DN - Daylight and Night hours (Romania Time Allocation-Romania)</t>
   </si>
   <si>
-    <t>92 Retail Management </t>
+    <t xml:space="preserve">92 Retail Management </t>
   </si>
   <si>
     <t>251 Management Retail</t>
@@ -237,40 +235,40 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <fonts count="5" x14ac:knownFonts="1">
     <font>
-      <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+      <sz val="11"/>
+      <name val="Calibri"/>
     </font>
     <font>
+      <color indexed="8"/>
+      <family val="2"/>
       <sz val="11"/>
-      <color indexed="8"/>
       <name val="Calibri"/>
-      <family val="2"/>
     </font>
     <font>
-      <sz val="11"/>
       <color rgb="FFFF0000"/>
-      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+      <sz val="11"/>
+      <name val="Calibri"/>
     </font>
     <font>
-      <sz val="11"/>
       <color rgb="FF000000"/>
-      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+      <sz val="11"/>
+      <name val="Calibri"/>
     </font>
     <font>
+      <family val="2"/>
+      <scheme val="minor"/>
       <sz val="11"/>
       <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="7">
@@ -282,24 +280,24 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.59999389629810485"/>
+        <fgColor theme="5" tint="0.5999938962981048"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="0" tint="-0.14999847407452621"/>
+        <fgColor theme="0" tint="-0.1499984740745262"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF00FF00"/>
+        <fgColor rgb="FFFF0000"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.79998168889431442"/>
+        <fgColor theme="5" tint="0.7999816888943144"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -325,27 +323,15 @@
       <right style="medium">
         <color indexed="64"/>
       </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
+      <top style="thin"/>
+      <bottom style="thin"/>
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
       <diagonal/>
     </border>
   </borders>
@@ -695,9 +681,9 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:BJ3"/>
-  <sheetFormatPr defaultRowHeight="15.65" customHeight="1" outlineLevelRow="1" x14ac:dyDescent="0.35"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:AG3"/>
+  <sheetFormatPr defaultRowHeight="15.65" outlineLevelRow="1" outlineLevelCol="0" x14ac:dyDescent="0.35" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="10.90625" style="1" customWidth="1"/>
     <col min="2" max="2" width="10.81640625" style="1" customWidth="1"/>
@@ -762,7 +748,7 @@
     <col min="63" max="63" width="16.08984375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:33" s="1" customFormat="1" ht="14.5" customHeight="1" outlineLevel="1" collapsed="1" x14ac:dyDescent="0.25">
+    <row r="1" ht="14.5" customHeight="1" spans="1:33" s="1" customFormat="1" x14ac:dyDescent="0.25" outlineLevel="1" collapsed="1">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -861,7 +847,7 @@
       </c>
       <c r="AG1" s="5"/>
     </row>
-    <row r="2" spans="1:33" s="1" customFormat="1" ht="15.65" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="2" ht="15.65" customHeight="1" spans="1:32" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>32</v>
       </c>
@@ -887,89 +873,89 @@
         <v>39</v>
       </c>
       <c r="I2" s="11">
-        <f ca="1">TODAY()-1</f>
+        <f>TODAY()-1</f>
         <v>45827</v>
       </c>
       <c r="J2" s="12" t="s">
         <v>40</v>
       </c>
       <c r="K2" s="12" t="s">
-        <v>33</v>
+        <v>41</v>
       </c>
       <c r="L2" s="11" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="M2" s="13" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="N2" s="11" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="O2" s="12" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="P2" s="14">
         <v>35</v>
       </c>
       <c r="Q2" s="15" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="R2" s="14" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="S2" s="16">
-        <f ca="1">I2+365</f>
+        <f>I2+365</f>
         <v>46192</v>
       </c>
       <c r="T2" s="12" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="U2" s="17" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="V2" s="11" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="W2" s="12" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="X2" s="11" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="Y2" s="16">
-        <f ca="1">I2+180</f>
+        <f>I2+180</f>
         <v>46007</v>
       </c>
       <c r="Z2" s="14" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="AA2" s="11">
-        <f ca="1">I2-1</f>
+        <f>I2-1</f>
         <v>45826</v>
       </c>
       <c r="AB2" t="s">
-        <v>33</v>
+        <v>41</v>
       </c>
       <c r="AC2" s="18" t="s">
+        <v>54</v>
+      </c>
+      <c r="AD2" s="11" t="s">
+        <v>55</v>
+      </c>
+      <c r="AE2" s="11">
+        <f>I2+365</f>
+        <v>46192</v>
+      </c>
+      <c r="AF2" s="14" t="s">
         <v>53</v>
       </c>
-      <c r="AD2" s="11" t="s">
-        <v>54</v>
-      </c>
-      <c r="AE2" s="11">
-        <f ca="1">I2+365</f>
-        <v>46192</v>
-      </c>
-      <c r="AF2" s="14" t="s">
-        <v>52</v>
-      </c>
     </row>
-    <row r="3" spans="1:33" s="1" customFormat="1" ht="15.65" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="3" ht="15.65" customHeight="1" spans="1:32" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>33</v>
+        <v>57</v>
       </c>
       <c r="C3" s="6" t="s">
         <v>34</v>
@@ -978,104 +964,110 @@
         <v>35</v>
       </c>
       <c r="E3" s="8" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="F3" s="9" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="G3" s="7" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="H3" s="10" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="I3" s="11">
-        <f ca="1">TODAY()-1</f>
+        <f>TODAY()-1</f>
         <v>45827</v>
       </c>
       <c r="J3" s="12" t="s">
         <v>40</v>
       </c>
       <c r="K3" s="12" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="L3" s="11" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="M3" s="11" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="N3" s="11" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="O3" s="12" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="P3" s="14">
         <v>40</v>
       </c>
       <c r="Q3" s="19" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="R3" s="14" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="S3" s="12" t="s">
-        <v>33</v>
+        <v>41</v>
       </c>
       <c r="T3" s="12" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="U3" s="20" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="V3" s="21" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="W3" s="12" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="X3" s="11" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="Y3" s="16">
-        <f ca="1">I3+180</f>
+        <f>I3+180</f>
         <v>46007</v>
       </c>
       <c r="Z3" s="14" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="AA3" s="11">
-        <f ca="1">I3-1</f>
+        <f>I3-1</f>
         <v>45826</v>
       </c>
       <c r="AB3" t="s">
-        <v>33</v>
+        <v>41</v>
       </c>
       <c r="AC3" s="18" t="s">
+        <v>54</v>
+      </c>
+      <c r="AD3" s="11" t="s">
+        <v>69</v>
+      </c>
+      <c r="AE3" s="11" t="s">
+        <v>41</v>
+      </c>
+      <c r="AF3" s="14" t="s">
         <v>53</v>
-      </c>
-      <c r="AD3" s="11" t="s">
-        <v>67</v>
-      </c>
-      <c r="AE3" s="11" t="s">
-        <v>33</v>
-      </c>
-      <c r="AF3" s="14" t="s">
-        <v>52</v>
       </c>
     </row>
   </sheetData>
-  <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AC2:AC3 O2:O3 J2:J3" xr:uid="{00000000-0002-0000-0000-000000000000}">
+  <dataValidations count="4">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AC2:AC3">
       <formula1>INDIRECT($E2)</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="S3" xr:uid="{00000000-0002-0000-0000-000003000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="J2:J3">
+      <formula1>INDIRECT($E2)</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="O2:O3">
+      <formula1>INDIRECT($E2)</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="S3">
       <formula1>INDIRECT($E2)</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" useFirstPageNumber="1" horizontalDpi="4294967295" verticalDpi="4294967295"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
   <headerFooter>
     <oddFooter>&amp;L_x000D_&amp;1#&amp;"Calibri"&amp;10&amp;K000000 EXPLEO Internal</oddFooter>
   </headerFooter>
